--- a/apps/staf-web/page/forms/sfari/2026-10-19_SFARI Calculator.xlsx
+++ b/apps/staf-web/page/forms/sfari/2026-10-19_SFARI Calculator.xlsx
@@ -1170,7 +1170,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1310,12 +1310,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF6F8FB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="76">
+  <borders count="78">
     <border>
       <left/>
       <right/>
@@ -2216,6 +2228,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2224,7 +2266,7 @@
     <xf numFmtId="0" fontId="9" fillId="17" borderId="54" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="386">
+  <cellXfs count="390">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
@@ -3323,13 +3365,25 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="29" fillId="24" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="29" fillId="26" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="30" fillId="24" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="30" fillId="26" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="30" fillId="24" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="30" fillId="26" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" horizontal="center"/>
     </xf>
   </cellXfs>
@@ -14273,104 +14327,104 @@
     </row>
     <row r="2" ht="18" customHeight="1"/>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="376" t="inlineStr">
+      <c r="A3" s="383" t="inlineStr">
         <is>
           <t xml:space="preserve">Reach name</t>
         </is>
       </c>
-      <c r="B3" s="377" t="str">
+      <c r="B3" s="385" t="str">
         <f>IF(ISBLANK(Scenario!B2),"",Scenario!B2)</f>
         <v/>
       </c>
-      <c r="C3" s="377"/>
-      <c r="D3" s="377"/>
+      <c r="C3" s="385"/>
+      <c r="D3" s="385"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="376" t="inlineStr">
+      <c r="A4" s="383" t="inlineStr">
         <is>
           <t xml:space="preserve">Assessment tier</t>
         </is>
       </c>
-      <c r="B4" s="377" t="inlineStr">
+      <c r="B4" s="386" t="inlineStr">
         <is>
           <t xml:space="preserve">Rapid</t>
         </is>
       </c>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
+      <c r="C4" s="386"/>
+      <c r="D4" s="386"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="376" t="inlineStr">
+      <c r="A5" s="383" t="inlineStr">
         <is>
           <t xml:space="preserve">Reach length</t>
         </is>
       </c>
-      <c r="B5" s="377" t="str">
+      <c r="B5" s="385" t="str">
         <f>IF(ISBLANK(Scenario!G2),"",Scenario!G2)</f>
         <v/>
       </c>
-      <c r="C5" s="377"/>
-      <c r="D5" s="377"/>
+      <c r="C5" s="385"/>
+      <c r="D5" s="385"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="376" t="inlineStr">
+      <c r="A6" s="383" t="inlineStr">
         <is>
           <t xml:space="preserve">Drainage area</t>
         </is>
       </c>
-      <c r="B6" s="377"/>
-      <c r="C6" s="377"/>
-      <c r="D6" s="377"/>
+      <c r="B6" s="384"/>
+      <c r="C6" s="384"/>
+      <c r="D6" s="384"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="376" t="inlineStr">
+      <c r="A7" s="383" t="inlineStr">
         <is>
           <t xml:space="preserve">Stream order (Strahler)</t>
         </is>
       </c>
-      <c r="B7" s="377"/>
-      <c r="C7" s="377"/>
-      <c r="D7" s="377"/>
+      <c r="B7" s="384"/>
+      <c r="C7" s="384"/>
+      <c r="D7" s="384"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="376" t="inlineStr">
+      <c r="A8" s="383" t="inlineStr">
         <is>
           <t xml:space="preserve">NARS-9 region</t>
         </is>
       </c>
-      <c r="B8" s="377"/>
-      <c r="C8" s="377"/>
-      <c r="D8" s="377"/>
+      <c r="B8" s="384"/>
+      <c r="C8" s="384"/>
+      <c r="D8" s="384"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="376" t="inlineStr">
+      <c r="A9" s="383" t="inlineStr">
         <is>
           <t xml:space="preserve">EPA Level I ecoregion</t>
         </is>
       </c>
-      <c r="B9" s="377"/>
-      <c r="C9" s="377"/>
-      <c r="D9" s="377"/>
+      <c r="B9" s="384"/>
+      <c r="C9" s="384"/>
+      <c r="D9" s="384"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="376" t="inlineStr">
+      <c r="A10" s="383" t="inlineStr">
         <is>
           <t xml:space="preserve">EPA Level II ecoregion</t>
         </is>
       </c>
-      <c r="B10" s="377"/>
-      <c r="C10" s="377"/>
-      <c r="D10" s="377"/>
+      <c r="B10" s="384"/>
+      <c r="C10" s="384"/>
+      <c r="D10" s="384"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="376" t="inlineStr">
+      <c r="A11" s="383" t="inlineStr">
         <is>
           <t xml:space="preserve">EPA Level III ecoregion</t>
         </is>
       </c>
-      <c r="B11" s="377"/>
-      <c r="C11" s="377"/>
-      <c r="D11" s="377"/>
+      <c r="B11" s="384"/>
+      <c r="C11" s="384"/>
+      <c r="D11" s="384"/>
     </row>
     <row r="12" ht="18" customHeight="1"/>
     <row r="13" ht="28" customHeight="1">
@@ -14402,7 +14456,7 @@
           <t xml:space="preserve">ECI</t>
         </is>
       </c>
-      <c r="B16" s="383" t="str">
+      <c r="B16" s="387" t="str">
         <f>IF(ISNUMBER(Scenario!$A$8),Scenario!$A$8,"")</f>
         <v/>
       </c>
@@ -14413,7 +14467,7 @@
           <t xml:space="preserve">Physical</t>
         </is>
       </c>
-      <c r="B17" s="384" t="str">
+      <c r="B17" s="388" t="str">
         <f>IF(ISNUMBER(Scenario!$C$8),Scenario!$C$8,"")</f>
         <v/>
       </c>
@@ -14424,7 +14478,7 @@
           <t xml:space="preserve">Chemical</t>
         </is>
       </c>
-      <c r="B18" s="384" t="str">
+      <c r="B18" s="388" t="str">
         <f>IF(ISNUMBER(Scenario!$C$56),Scenario!$C$56,"")</f>
         <v/>
       </c>
@@ -14435,7 +14489,7 @@
           <t xml:space="preserve">Biological</t>
         </is>
       </c>
-      <c r="B19" s="384" t="str">
+      <c r="B19" s="388" t="str">
         <f>IF(ISNUMBER(Scenario!$C$72),Scenario!$C$72,"")</f>
         <v/>
       </c>
@@ -14454,7 +14508,7 @@
           <t xml:space="preserve">Catchment hydrology</t>
         </is>
       </c>
-      <c r="B21" s="385" t="str">
+      <c r="B21" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$8),Scenario!$H$8,"")</f>
         <v/>
       </c>
@@ -14465,7 +14519,7 @@
           <t xml:space="preserve">Surface water storage</t>
         </is>
       </c>
-      <c r="B22" s="385" t="str">
+      <c r="B22" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$12),Scenario!$H$12,"")</f>
         <v/>
       </c>
@@ -14476,7 +14530,7 @@
           <t xml:space="preserve">Reach inflow</t>
         </is>
       </c>
-      <c r="B23" s="385" t="str">
+      <c r="B23" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$16),Scenario!$H$16,"")</f>
         <v/>
       </c>
@@ -14487,7 +14541,7 @@
           <t xml:space="preserve">Streamflow regime</t>
         </is>
       </c>
-      <c r="B24" s="385" t="str">
+      <c r="B24" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$20),Scenario!$H$20,"")</f>
         <v/>
       </c>
@@ -14506,7 +14560,7 @@
           <t xml:space="preserve">Low flow and baseflow dynamics</t>
         </is>
       </c>
-      <c r="B26" s="385" t="str">
+      <c r="B26" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$24),Scenario!$H$24,"")</f>
         <v/>
       </c>
@@ -14517,7 +14571,7 @@
           <t xml:space="preserve">High flow dynamics</t>
         </is>
       </c>
-      <c r="B27" s="385" t="str">
+      <c r="B27" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$28),Scenario!$H$28,"")</f>
         <v/>
       </c>
@@ -14528,7 +14582,7 @@
           <t xml:space="preserve">Floodplain connectivity</t>
         </is>
       </c>
-      <c r="B28" s="385" t="str">
+      <c r="B28" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$32),Scenario!$H$32,"")</f>
         <v/>
       </c>
@@ -14539,7 +14593,7 @@
           <t xml:space="preserve">Hyporheic connectivity</t>
         </is>
       </c>
-      <c r="B29" s="385" t="str">
+      <c r="B29" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$36),Scenario!$H$36,"")</f>
         <v/>
       </c>
@@ -14558,7 +14612,7 @@
           <t xml:space="preserve">Channel evolution</t>
         </is>
       </c>
-      <c r="B31" s="385" t="str">
+      <c r="B31" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$40),Scenario!$H$40,"")</f>
         <v/>
       </c>
@@ -14569,7 +14623,7 @@
           <t xml:space="preserve">Channel and floodplain dynamics</t>
         </is>
       </c>
-      <c r="B32" s="385" t="str">
+      <c r="B32" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$44),Scenario!$H$44,"")</f>
         <v/>
       </c>
@@ -14580,7 +14634,7 @@
           <t xml:space="preserve">Sediment continuity</t>
         </is>
       </c>
-      <c r="B33" s="385" t="str">
+      <c r="B33" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$48),Scenario!$H$48,"")</f>
         <v/>
       </c>
@@ -14591,7 +14645,7 @@
           <t xml:space="preserve">Bed composition and bedform dynamics</t>
         </is>
       </c>
-      <c r="B34" s="385" t="str">
+      <c r="B34" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$52),Scenario!$H$52,"")</f>
         <v/>
       </c>
@@ -14610,7 +14664,7 @@
           <t xml:space="preserve">Light and thermal regime</t>
         </is>
       </c>
-      <c r="B36" s="385" t="str">
+      <c r="B36" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$56),Scenario!$H$56,"")</f>
         <v/>
       </c>
@@ -14621,7 +14675,7 @@
           <t xml:space="preserve">Carbon processing</t>
         </is>
       </c>
-      <c r="B37" s="385" t="str">
+      <c r="B37" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$60),Scenario!$H$60,"")</f>
         <v/>
       </c>
@@ -14632,7 +14686,7 @@
           <t xml:space="preserve">Nutrient cycling</t>
         </is>
       </c>
-      <c r="B38" s="385" t="str">
+      <c r="B38" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$64),Scenario!$H$64,"")</f>
         <v/>
       </c>
@@ -14643,7 +14697,7 @@
           <t xml:space="preserve">Water and soil quality</t>
         </is>
       </c>
-      <c r="B39" s="385" t="str">
+      <c r="B39" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$68),Scenario!$H$68,"")</f>
         <v/>
       </c>
@@ -14662,7 +14716,7 @@
           <t xml:space="preserve">Habitat provision</t>
         </is>
       </c>
-      <c r="B41" s="385" t="str">
+      <c r="B41" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$72),Scenario!$H$72,"")</f>
         <v/>
       </c>
@@ -14673,7 +14727,7 @@
           <t xml:space="preserve">Population support</t>
         </is>
       </c>
-      <c r="B42" s="385" t="str">
+      <c r="B42" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$76),Scenario!$H$76,"")</f>
         <v/>
       </c>
@@ -14684,7 +14738,7 @@
           <t xml:space="preserve">Community dynamics</t>
         </is>
       </c>
-      <c r="B43" s="385" t="str">
+      <c r="B43" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$80),Scenario!$H$80,"")</f>
         <v/>
       </c>
@@ -14695,7 +14749,7 @@
           <t xml:space="preserve">Watershed connectivity</t>
         </is>
       </c>
-      <c r="B44" s="385" t="str">
+      <c r="B44" s="389" t="str">
         <f>IF(ISNUMBER(Scenario!$H$84),Scenario!$H$84,"")</f>
         <v/>
       </c>
